--- a/pdf2img/tabel/table_4.xlsx
+++ b/pdf2img/tabel/table_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,82 +432,104 @@
       <c r="E1" t="n">
         <v>4</v>
       </c>
+      <c r="F1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPRORAN</t>
+          <t>LAPORAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TRANSAKSL</t>
+          <t>TRANSAKSI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SPOT,DAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DAN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>DERIVATIE</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Per,31/Desember,2025</t>
+          <t>[Per,31]Desember,2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(dalam</t>
+          <t>{</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>dalam</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>jutaan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>rupiah</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>}</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>|</t>
+          <t>TRANSAKSI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>_TRANSAKS!</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Nilai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -525,340 +547,351 @@
           <t>Liabilitas</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Derivatif</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRANSAKSI</t>
+          <t>Derivatif</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NO.</t>
+          <t>'</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nilai</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ons</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Notional</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>args</t>
-        </is>
-      </c>
+          <t>Liabilitas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liabilitas</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>Terkait</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nilai</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tukar</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nilai</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tukar</t>
-        </is>
-      </c>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spot</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jual</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jual</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Beli</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a.</t>
+          <t>Future</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Beli</t>
-        </is>
-      </c>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swap</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Terkait</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dengan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Suku</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bunga</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Terkait</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>dengan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Suku</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Bunga</t>
-        </is>
-      </c>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Forward</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>a.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jual</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>b.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Beli</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>a.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Jual</t>
-        </is>
-      </c>
+          <t>Future</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>b.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Beli</t>
-        </is>
-      </c>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Future</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swap</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Lainnya</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ae</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>es</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>De</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ge</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
           <t>JUMLAH</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
